--- a/data/trans_camb/P68-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P68-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,77; -3,18</t>
+          <t>-22,89; -1,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 8,87</t>
+          <t>-14,53; 8,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,32; -6,57</t>
+          <t>-27,65; -6,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 6,41</t>
+          <t>-10,33; 6,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 7,48</t>
+          <t>-9,64; 7,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 19,59</t>
+          <t>-6,84; 18,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,47; -2,13</t>
+          <t>-15,33; -2,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 4,58</t>
+          <t>-10,74; 3,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 2,11</t>
+          <t>-15,41; 1,38</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-74,25; -12,46</t>
+          <t>-76,39; -1,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,38; 39,51</t>
+          <t>-50,25; 41,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-93,64; -12,79</t>
+          <t>-93,06; -19,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,1; 62,25</t>
+          <t>-62,11; 65,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 75,15</t>
+          <t>-56,31; 80,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 179,0</t>
+          <t>-45,38; 158,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,61; -9,55</t>
+          <t>-65,51; -11,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,48; 26,01</t>
+          <t>-46,87; 19,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,45; 11,95</t>
+          <t>-66,16; 8,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 2,76</t>
+          <t>-8,31; 2,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 3,71</t>
+          <t>-7,77; 4,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,81; -1,85</t>
+          <t>-14,73; -2,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 8,13</t>
+          <t>-6,56; 7,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 0,12</t>
+          <t>-12,79; -0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -1,99</t>
+          <t>-18,28; -1,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 3,13</t>
+          <t>-5,78; 3,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 0,36</t>
+          <t>-8,35; 0,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,88; -3,91</t>
+          <t>-14,79; -4,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 11,39</t>
+          <t>-28,87; 12,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 15,92</t>
+          <t>-26,91; 19,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,07; -6,86</t>
+          <t>-53,3; -8,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,4; 39,76</t>
+          <t>-25,03; 37,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,72; 0,53</t>
+          <t>-49,41; -1,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,18; -10,04</t>
+          <t>-68,22; -7,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 13,83</t>
+          <t>-21,6; 14,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 1,7</t>
+          <t>-31,42; 3,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,35; -16,34</t>
+          <t>-56,27; -18,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 6,53</t>
+          <t>-4,73; 6,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 7,6</t>
+          <t>-2,74; 7,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 3,5</t>
+          <t>-6,71; 3,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 9,74</t>
+          <t>-4,48; 10,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 6,58</t>
+          <t>-6,79; 7,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 4,35</t>
+          <t>-7,8; 4,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 5,57</t>
+          <t>-2,75; 6,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 5,58</t>
+          <t>-3,36; 5,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 2,34</t>
+          <t>-5,25; 2,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 31,75</t>
+          <t>-18,95; 31,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 38,9</t>
+          <t>-10,97; 37,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 17,19</t>
+          <t>-26,41; 17,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 50,85</t>
+          <t>-16,84; 54,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 34,75</t>
+          <t>-26,27; 37,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 23,04</t>
+          <t>-28,77; 24,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 26,96</t>
+          <t>-11,63; 29,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 26,77</t>
+          <t>-13,34; 27,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 11,36</t>
+          <t>-21,44; 12,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 5,83</t>
+          <t>-7,23; 5,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 6,08</t>
+          <t>-8,17; 5,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,72; -2,12</t>
+          <t>-24,06; -1,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 4,58</t>
+          <t>-12,32; 5,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 9,28</t>
+          <t>-6,16; 9,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 27,87</t>
+          <t>4,4; 29,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 2,53</t>
+          <t>-7,59; 3,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 4,62</t>
+          <t>-5,17; 5,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 5,46</t>
+          <t>-15,97; 5,79</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 26,22</t>
+          <t>-25,31; 24,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 26,68</t>
+          <t>-27,13; 23,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-76,41; -9,28</t>
+          <t>-79,16; -7,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,34; 27,85</t>
+          <t>-47,11; 30,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 55,24</t>
+          <t>-23,51; 55,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,4; 158,44</t>
+          <t>12,31; 156,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 11,36</t>
+          <t>-27,42; 13,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 21,51</t>
+          <t>-19,29; 23,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,79; 23,71</t>
+          <t>-57,52; 24,34</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 9,49</t>
+          <t>-9,89; 9,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 9,27</t>
+          <t>-11,05; 9,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 2,88</t>
+          <t>-13,62; 3,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 29,05</t>
+          <t>-1,73; 29,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 21,51</t>
+          <t>-4,98; 22,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 15,45</t>
+          <t>-7,48; 14,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 12,19</t>
+          <t>-4,44; 12,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 9,93</t>
+          <t>-6,32; 9,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 4,82</t>
+          <t>-8,62; 4,04</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 41,73</t>
+          <t>-30,44; 40,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 41,26</t>
+          <t>-33,84; 42,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 13,62</t>
+          <t>-40,8; 14,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 197,31</t>
+          <t>-8,74; 213,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 157,88</t>
+          <t>-18,85; 165,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 116,63</t>
+          <t>-24,2; 120,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 54,78</t>
+          <t>-14,74; 54,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 43,26</t>
+          <t>-21,25; 46,5</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 22,68</t>
+          <t>-26,96; 18,83</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,17; 35,42</t>
+          <t>6,63; 39,23</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,63; 30,74</t>
+          <t>7,66; 32,04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,68</t>
+          <t>0,0; 48,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8,98; 28,8</t>
+          <t>8,8; 28,56</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,7</t>
+          <t>-4,52; 1,51</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,84</t>
+          <t>-3,12; 3,26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,94; -3,5</t>
+          <t>-13,97; -3,54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,88</t>
+          <t>-2,52; 5,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,13</t>
+          <t>-4,14; 2,75</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 9,03</t>
+          <t>-1,67; 8,79</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,95</t>
+          <t>-2,88; 1,93</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,86</t>
+          <t>-2,87; 1,84</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -0,26</t>
+          <t>-7,81; -0,16</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 7,19</t>
+          <t>-17,35; 6,24</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 11,95</t>
+          <t>-11,86; 14,06</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-53,73; -14,91</t>
+          <t>-54,49; -14,68</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 24,42</t>
+          <t>-10,73; 25,53</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 16,29</t>
+          <t>-17,82; 13,79</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 44,25</t>
+          <t>-7,71; 43,07</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 8,58</t>
+          <t>-11,55; 8,51</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 8,37</t>
+          <t>-11,69; 8,21</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-32,4; -1,14</t>
+          <t>-32,81; -1,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P68-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P68-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-19,03</t>
+          <t>-16,82</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,23</t>
+          <t>3,61</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,74</t>
+          <t>-7,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,89; -1,25</t>
+          <t>-22,69; -3,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 8,67</t>
+          <t>-15,81; 7,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,65; -6,53</t>
+          <t>-27,05; -3,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 6,68</t>
+          <t>-11,04; 5,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 7,48</t>
+          <t>-10,13; 7,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 18,37</t>
+          <t>-6,75; 17,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,33; -2,35</t>
+          <t>-14,96; -2,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 3,65</t>
+          <t>-10,02; 4,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 1,38</t>
+          <t>-14,97; 1,55</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-72,76%</t>
+          <t>-64,32%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-37,24%</t>
+          <t>-35,96%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-76,39; -1,41</t>
+          <t>-76,4; -14,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 41,64</t>
+          <t>-53,25; 35,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-93,06; -19,77</t>
+          <t>-90,35; -5,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-62,11; 65,04</t>
+          <t>-61,93; 61,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,31; 80,0</t>
+          <t>-57,38; 76,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,38; 158,31</t>
+          <t>-41,34; 150,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,51; -11,0</t>
+          <t>-65,0; -11,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,87; 19,53</t>
+          <t>-44,91; 26,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,16; 8,1</t>
+          <t>-66,68; 8,58</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-8,4</t>
+          <t>-7,72</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,96</t>
+          <t>-6,9</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-8,95</t>
+          <t>-7,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 2,53</t>
+          <t>-8,42; 3,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 4,42</t>
+          <t>-7,32; 4,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,73; -2,1</t>
+          <t>-13,82; -0,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 7,63</t>
+          <t>-5,83; 8,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,79; -0,3</t>
+          <t>-13,64; -0,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -1,32</t>
+          <t>-13,7; -1,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 3,38</t>
+          <t>-6,13; 3,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 0,67</t>
+          <t>-8,52; 0,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,79; -4,21</t>
+          <t>-12,05; -2,86</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-32,85%</t>
+          <t>-30,18%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-38,31%</t>
+          <t>-29,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-36,17%</t>
+          <t>-30,31%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 12,72</t>
+          <t>-30,14; 12,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 19,74</t>
+          <t>-26,51; 20,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,3; -8,44</t>
+          <t>-50,47; -3,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 37,7</t>
+          <t>-22,6; 41,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,41; -1,42</t>
+          <t>-49,83; 0,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,22; -7,72</t>
+          <t>-52,26; -5,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 14,53</t>
+          <t>-22,33; 13,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 3,37</t>
+          <t>-31,62; 2,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,27; -18,08</t>
+          <t>-45,75; -12,85</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-1,87</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-1,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 6,46</t>
+          <t>-4,21; 6,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 7,6</t>
+          <t>-3,28; 7,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 3,76</t>
+          <t>-7,65; 3,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 10,25</t>
+          <t>-3,73; 9,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 7,09</t>
+          <t>-6,62; 6,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 4,54</t>
+          <t>-7,06; 5,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 6,08</t>
+          <t>-2,74; 5,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 5,69</t>
+          <t>-3,25; 5,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 2,53</t>
+          <t>-5,29; 2,39</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-7,06%</t>
+          <t>-8,33%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-5,37%</t>
+          <t>-4,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-6,16%</t>
+          <t>-6,36%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 31,17</t>
+          <t>-17,2; 33,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 37,37</t>
+          <t>-13,25; 41,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 17,97</t>
+          <t>-30,01; 14,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 54,91</t>
+          <t>-14,8; 51,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 37,26</t>
+          <t>-25,42; 33,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 24,09</t>
+          <t>-26,5; 28,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 29,36</t>
+          <t>-11,51; 27,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 27,91</t>
+          <t>-13,31; 25,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 12,45</t>
+          <t>-21,75; 12,16</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-11,07</t>
+          <t>-3,38</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,62</t>
+          <t>6,29</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>0,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 5,59</t>
+          <t>-7,22; 5,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 5,48</t>
+          <t>-7,32; 5,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-24,06; -1,94</t>
+          <t>-9,22; 2,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 5,33</t>
+          <t>-11,32; 5,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 9,67</t>
+          <t>-7,21; 10,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 29,38</t>
+          <t>-1,19; 13,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 3,19</t>
+          <t>-7,84; 2,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 5,08</t>
+          <t>-5,31; 4,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 5,79</t>
+          <t>-3,85; 4,7</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-43,06%</t>
+          <t>-13,14%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-10,17%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 24,35</t>
+          <t>-25,2; 24,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 23,25</t>
+          <t>-25,49; 24,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,16; -7,21</t>
+          <t>-30,75; 13,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,11; 30,64</t>
+          <t>-44,29; 33,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 55,04</t>
+          <t>-27,0; 59,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,31; 156,27</t>
+          <t>-4,71; 77,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 13,83</t>
+          <t>-28,38; 11,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 23,29</t>
+          <t>-19,71; 21,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-57,52; 24,34</t>
+          <t>-14,03; 22,04</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-5,33</t>
+          <t>-5,9</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,3</t>
+          <t>5,11</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-2,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 9,47</t>
+          <t>-9,28; 10,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 9,55</t>
+          <t>-10,69; 9,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 3,39</t>
+          <t>-14,75; 1,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 29,52</t>
+          <t>-2,62; 28,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 22,93</t>
+          <t>-6,28; 22,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 14,9</t>
+          <t>-6,56; 15,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 12,07</t>
+          <t>-3,91; 11,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 9,87</t>
+          <t>-5,39; 9,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 4,04</t>
+          <t>-8,47; 4,47</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-18,95%</t>
+          <t>-20,99%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-6,83%</t>
+          <t>-8,33%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 40,06</t>
+          <t>-28,25; 45,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-33,84; 42,08</t>
+          <t>-32,8; 39,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,8; 14,4</t>
+          <t>-42,7; 6,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 213,11</t>
+          <t>-10,63; 196,99</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 165,29</t>
+          <t>-22,32; 156,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 120,78</t>
+          <t>-19,81; 137,25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 54,54</t>
+          <t>-13,32; 54,2</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 46,5</t>
+          <t>-18,61; 44,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 18,83</t>
+          <t>-27,59; 20,62</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17,25</t>
+          <t>19,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,41</t>
+          <t>15,21</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,82</t>
+          <t>17,15</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,64</t>
+          <t>0,0; 78,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,63; 39,23</t>
+          <t>7,3; 40,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,66; 32,04</t>
+          <t>6,85; 30,83</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,75</t>
+          <t>0,0; 47,82</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8,8; 28,56</t>
+          <t>9,2; 28,66</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-7,45</t>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,27</t>
+          <t>-2,28</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 1,51</t>
+          <t>-4,63; 1,19</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 3,26</t>
+          <t>-3,41; 2,8</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,97; -3,54</t>
+          <t>-7,93; -1,87</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 5,0</t>
+          <t>-2,41; 5,15</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 2,75</t>
+          <t>-4,28; 2,9</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 8,79</t>
+          <t>-1,58; 4,59</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,93</t>
+          <t>-3,19; 1,71</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,84</t>
+          <t>-2,93; 1,91</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -0,16</t>
+          <t>-4,54; -0,17</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-29,88%</t>
+          <t>-19,05%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-13,76%</t>
+          <t>-9,6%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 6,24</t>
+          <t>-17,71; 5,1</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 14,06</t>
+          <t>-12,86; 11,97</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-54,49; -14,68</t>
+          <t>-30,64; -8,17</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 25,53</t>
+          <t>-10,42; 26,19</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 13,79</t>
+          <t>-18,15; 15,28</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 43,07</t>
+          <t>-6,63; 23,49</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 8,51</t>
+          <t>-12,67; 7,55</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 8,21</t>
+          <t>-11,97; 8,49</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-32,81; -1,07</t>
+          <t>-18,03; -0,74</t>
         </is>
       </c>
     </row>
